--- a/src/test/resources/testData/registration_negative_testdata.xlsx
+++ b/src/test/resources/testData/registration_negative_testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuyen_2251061919\Nam4\DATN\opencart-automation-framework\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E35298-15EB-4526-85C7-06DB223203A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7283E7C-0DC8-49B2-B27E-289FAAE4D204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>FirstName</t>
   </si>
@@ -51,27 +51,15 @@
     <t>SubscribeNewsletter</t>
   </si>
   <si>
-    <t>test@gmail.com</t>
-  </si>
-  <si>
-    <t>Văn A</t>
-  </si>
-  <si>
     <t>Aa123456</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Expected</t>
   </si>
   <si>
     <t>First Name must be between 1 and 32 characters!</t>
   </si>
   <si>
-    <t>TCID</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -79,13 +67,103 @@
   </si>
   <si>
     <t>Nguyen</t>
+  </si>
+  <si>
+    <t>Van A</t>
+  </si>
+  <si>
+    <t>E-Mail Address does not appear to be valid!</t>
+  </si>
+  <si>
+    <t>Telephone must be between 3 and 32 characters!</t>
+  </si>
+  <si>
+    <t>Hoang</t>
+  </si>
+  <si>
+    <t>Thao</t>
+  </si>
+  <si>
+    <t>Minh</t>
+  </si>
+  <si>
+    <t>Anh</t>
+  </si>
+  <si>
+    <t>Ngoc</t>
+  </si>
+  <si>
+    <t>Mai</t>
+  </si>
+  <si>
+    <t>vana@gmail.com</t>
+  </si>
+  <si>
+    <t>hoanganh@gmail.com</t>
+  </si>
+  <si>
+    <t>minhanh@gmail.com</t>
+  </si>
+  <si>
+    <t>ngocmai12@gmail.com</t>
+  </si>
+  <si>
+    <t>0345677789</t>
+  </si>
+  <si>
+    <t>0345677790</t>
+  </si>
+  <si>
+    <t>0345677791</t>
+  </si>
+  <si>
+    <t>0345677793</t>
+  </si>
+  <si>
+    <t>Password must be between 4 and 20 characters!</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Expected Error Field</t>
+  </si>
+  <si>
+    <t>firstname</t>
+  </si>
+  <si>
+    <t>lastname</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>telephone</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>RG_02_1</t>
+  </si>
+  <si>
+    <t>RG_02_2</t>
+  </si>
+  <si>
+    <t>RG_02_3</t>
+  </si>
+  <si>
+    <t>RG_02_4</t>
+  </si>
+  <si>
+    <t>RG_02_5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +183,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -114,7 +199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,13 +207,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,107 +514,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="22.77734375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="9" width="22.77734375" style="1"/>
-    <col min="10" max="10" width="52.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="22.77734375" style="1"/>
+    <col min="1" max="1" width="13.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="22.77734375" style="1"/>
+    <col min="5" max="5" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="22.77734375" style="1"/>
+    <col min="9" max="9" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" style="1" customWidth="1"/>
+    <col min="11" max="11" width="55.109375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="22.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="K4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1">
-        <v>123456789</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1">
-        <v>123456789</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
+      <c r="J6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="F2:F4 F6" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>